--- a/ig/main/CodeSystem-1.2.250.1.213.1.1.4.322.xlsx
+++ b/ig/main/CodeSystem-1.2.250.1.213.1.1.4.322.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5221" uniqueCount="3469">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5224" uniqueCount="3471">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20241217000000</t>
+    <t>202412180000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-17T13:44:59-00:00</t>
+    <t>2024-12-18T17:48:28-00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -121,6 +121,12 @@
   </si>
   <si>
     <t>1</t>
+  </si>
+  <si>
+    <t>D0009-6</t>
+  </si>
+  <si>
+    <t>Paroi Libre de l’OD</t>
   </si>
   <si>
     <t>D0009-7</t>
@@ -10717,7 +10723,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D1729"/>
+  <dimension ref="A1:D1730"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -11798,7 +11804,7 @@
         <v>212</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>19</v>
+        <v>213</v>
       </c>
       <c r="D90" s="2"/>
     </row>
@@ -11807,10 +11813,10 @@
         <v>35</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>214</v>
+        <v>19</v>
       </c>
       <c r="D91" s="2"/>
     </row>
@@ -15602,7 +15608,7 @@
         <v>845</v>
       </c>
       <c r="C407" t="s" s="2">
-        <v>111</v>
+        <v>846</v>
       </c>
       <c r="D407" s="2"/>
     </row>
@@ -15611,10 +15617,10 @@
         <v>35</v>
       </c>
       <c r="B408" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="C408" t="s" s="2">
-        <v>847</v>
+        <v>113</v>
       </c>
       <c r="D408" s="2"/>
     </row>
@@ -23030,7 +23036,7 @@
         <v>2082</v>
       </c>
       <c r="C1026" t="s" s="2">
-        <v>1961</v>
+        <v>2083</v>
       </c>
       <c r="D1026" s="2"/>
     </row>
@@ -23039,7 +23045,7 @@
         <v>35</v>
       </c>
       <c r="B1027" t="s" s="2">
-        <v>2083</v>
+        <v>2084</v>
       </c>
       <c r="C1027" t="s" s="2">
         <v>1963</v>
@@ -23051,7 +23057,7 @@
         <v>35</v>
       </c>
       <c r="B1028" t="s" s="2">
-        <v>2084</v>
+        <v>2085</v>
       </c>
       <c r="C1028" t="s" s="2">
         <v>1965</v>
@@ -23063,7 +23069,7 @@
         <v>35</v>
       </c>
       <c r="B1029" t="s" s="2">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="C1029" t="s" s="2">
         <v>1967</v>
@@ -23075,7 +23081,7 @@
         <v>35</v>
       </c>
       <c r="B1030" t="s" s="2">
-        <v>2086</v>
+        <v>2087</v>
       </c>
       <c r="C1030" t="s" s="2">
         <v>1969</v>
@@ -23087,7 +23093,7 @@
         <v>35</v>
       </c>
       <c r="B1031" t="s" s="2">
-        <v>2087</v>
+        <v>2088</v>
       </c>
       <c r="C1031" t="s" s="2">
         <v>1971</v>
@@ -23099,7 +23105,7 @@
         <v>35</v>
       </c>
       <c r="B1032" t="s" s="2">
-        <v>2088</v>
+        <v>2089</v>
       </c>
       <c r="C1032" t="s" s="2">
         <v>1973</v>
@@ -23111,7 +23117,7 @@
         <v>35</v>
       </c>
       <c r="B1033" t="s" s="2">
-        <v>2089</v>
+        <v>2090</v>
       </c>
       <c r="C1033" t="s" s="2">
         <v>1975</v>
@@ -23123,10 +23129,10 @@
         <v>35</v>
       </c>
       <c r="B1034" t="s" s="2">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="C1034" t="s" s="2">
-        <v>2091</v>
+        <v>1977</v>
       </c>
       <c r="D1034" s="2"/>
     </row>
@@ -23258,7 +23264,7 @@
         <v>2112</v>
       </c>
       <c r="C1045" t="s" s="2">
-        <v>644</v>
+        <v>2113</v>
       </c>
       <c r="D1045" s="2"/>
     </row>
@@ -23267,7 +23273,7 @@
         <v>35</v>
       </c>
       <c r="B1046" t="s" s="2">
-        <v>2113</v>
+        <v>2114</v>
       </c>
       <c r="C1046" t="s" s="2">
         <v>646</v>
@@ -23279,10 +23285,10 @@
         <v>35</v>
       </c>
       <c r="B1047" t="s" s="2">
-        <v>2114</v>
+        <v>2115</v>
       </c>
       <c r="C1047" t="s" s="2">
-        <v>2115</v>
+        <v>648</v>
       </c>
       <c r="D1047" s="2"/>
     </row>
@@ -23822,7 +23828,7 @@
         <v>2204</v>
       </c>
       <c r="C1092" t="s" s="2">
-        <v>2159</v>
+        <v>2205</v>
       </c>
       <c r="D1092" s="2"/>
     </row>
@@ -23831,10 +23837,10 @@
         <v>35</v>
       </c>
       <c r="B1093" t="s" s="2">
-        <v>2205</v>
+        <v>2206</v>
       </c>
       <c r="C1093" t="s" s="2">
-        <v>2206</v>
+        <v>2161</v>
       </c>
       <c r="D1093" s="2"/>
     </row>
@@ -24326,7 +24332,7 @@
         <v>2287</v>
       </c>
       <c r="C1134" t="s" s="2">
-        <v>2137</v>
+        <v>2288</v>
       </c>
       <c r="D1134" s="2"/>
     </row>
@@ -24335,10 +24341,10 @@
         <v>35</v>
       </c>
       <c r="B1135" t="s" s="2">
-        <v>2288</v>
+        <v>2289</v>
       </c>
       <c r="C1135" t="s" s="2">
-        <v>2289</v>
+        <v>2139</v>
       </c>
       <c r="D1135" s="2"/>
     </row>
@@ -24374,7 +24380,7 @@
         <v>2294</v>
       </c>
       <c r="C1138" t="s" s="2">
-        <v>1115</v>
+        <v>2295</v>
       </c>
       <c r="D1138" s="2"/>
     </row>
@@ -24383,10 +24389,10 @@
         <v>35</v>
       </c>
       <c r="B1139" t="s" s="2">
-        <v>2295</v>
+        <v>2296</v>
       </c>
       <c r="C1139" t="s" s="2">
-        <v>2296</v>
+        <v>1117</v>
       </c>
       <c r="D1139" s="2"/>
     </row>
@@ -25838,7 +25844,7 @@
         <v>2537</v>
       </c>
       <c r="C1260" t="s" s="2">
-        <v>2486</v>
+        <v>2538</v>
       </c>
       <c r="D1260" s="2"/>
     </row>
@@ -25847,10 +25853,10 @@
         <v>35</v>
       </c>
       <c r="B1261" t="s" s="2">
-        <v>2538</v>
+        <v>2539</v>
       </c>
       <c r="C1261" t="s" s="2">
-        <v>2539</v>
+        <v>2488</v>
       </c>
       <c r="D1261" s="2"/>
     </row>
@@ -28154,7 +28160,7 @@
         <v>2922</v>
       </c>
       <c r="C1453" t="s" s="2">
-        <v>2875</v>
+        <v>2923</v>
       </c>
       <c r="D1453" s="2"/>
     </row>
@@ -28163,10 +28169,10 @@
         <v>35</v>
       </c>
       <c r="B1454" t="s" s="2">
-        <v>2923</v>
+        <v>2924</v>
       </c>
       <c r="C1454" t="s" s="2">
-        <v>2924</v>
+        <v>2877</v>
       </c>
       <c r="D1454" s="2"/>
     </row>
@@ -28610,7 +28616,7 @@
         <v>2997</v>
       </c>
       <c r="C1491" t="s" s="2">
-        <v>320</v>
+        <v>2998</v>
       </c>
       <c r="D1491" s="2"/>
     </row>
@@ -28619,10 +28625,10 @@
         <v>35</v>
       </c>
       <c r="B1492" t="s" s="2">
-        <v>2998</v>
+        <v>2999</v>
       </c>
       <c r="C1492" t="s" s="2">
-        <v>2999</v>
+        <v>322</v>
       </c>
       <c r="D1492" s="2"/>
     </row>
@@ -28778,7 +28784,7 @@
         <v>3024</v>
       </c>
       <c r="C1505" t="s" s="2">
-        <v>77</v>
+        <v>3025</v>
       </c>
       <c r="D1505" s="2"/>
     </row>
@@ -28787,7 +28793,7 @@
         <v>35</v>
       </c>
       <c r="B1506" t="s" s="2">
-        <v>3025</v>
+        <v>3026</v>
       </c>
       <c r="C1506" t="s" s="2">
         <v>79</v>
@@ -28799,7 +28805,7 @@
         <v>35</v>
       </c>
       <c r="B1507" t="s" s="2">
-        <v>3026</v>
+        <v>3027</v>
       </c>
       <c r="C1507" t="s" s="2">
         <v>81</v>
@@ -28811,10 +28817,10 @@
         <v>35</v>
       </c>
       <c r="B1508" t="s" s="2">
-        <v>3027</v>
+        <v>3028</v>
       </c>
       <c r="C1508" t="s" s="2">
-        <v>3028</v>
+        <v>83</v>
       </c>
       <c r="D1508" s="2"/>
     </row>
@@ -29246,7 +29252,7 @@
         <v>3099</v>
       </c>
       <c r="C1544" t="s" s="2">
-        <v>1769</v>
+        <v>3100</v>
       </c>
       <c r="D1544" s="2"/>
     </row>
@@ -29255,10 +29261,10 @@
         <v>35</v>
       </c>
       <c r="B1545" t="s" s="2">
-        <v>3100</v>
+        <v>3101</v>
       </c>
       <c r="C1545" t="s" s="2">
-        <v>3101</v>
+        <v>1771</v>
       </c>
       <c r="D1545" s="2"/>
     </row>
@@ -30338,7 +30344,7 @@
         <v>3280</v>
       </c>
       <c r="C1635" t="s" s="2">
-        <v>3105</v>
+        <v>3281</v>
       </c>
       <c r="D1635" s="2"/>
     </row>
@@ -30347,10 +30353,10 @@
         <v>35</v>
       </c>
       <c r="B1636" t="s" s="2">
-        <v>3281</v>
+        <v>3282</v>
       </c>
       <c r="C1636" t="s" s="2">
-        <v>3282</v>
+        <v>3107</v>
       </c>
       <c r="D1636" s="2"/>
     </row>
@@ -31469,6 +31475,18 @@
         <v>3468</v>
       </c>
       <c r="D1729" s="2"/>
+    </row>
+    <row r="1730">
+      <c r="A1730" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B1730" t="s" s="2">
+        <v>3469</v>
+      </c>
+      <c r="C1730" t="s" s="2">
+        <v>3470</v>
+      </c>
+      <c r="D1730" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
